--- a/捷徑/大量傷患權限/附件1、大量傷病患系統開通清冊(三大).xlsx
+++ b/捷徑/大量傷患權限/附件1、大量傷病患系統開通清冊(三大).xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2.救護科\115年\一站通-大傷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ClaudeCode\EMS_System\捷徑\大量傷患權限\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE44DA1-94AC-467F-B9BD-E3BB4EC12169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FB7DE4-2AAE-40B5-9272-57E1C0365FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="82">
   <si>
     <t>單位</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,19 +83,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>第三大隊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何幸家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>幹部</t>
-  </si>
-  <si>
-    <t>張育綸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>大竹分隊</t>
@@ -406,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -429,20 +416,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -454,9 +432,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -745,18 +720,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="15.5546875" customWidth="1"/>
+    <col min="1" max="3" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4" ht="21.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -771,22 +746,22 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>13</v>
@@ -795,10 +770,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>13</v>
@@ -807,10 +782,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>13</v>
@@ -819,10 +794,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>13</v>
@@ -831,34 +806,34 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -867,19 +842,19 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>73</v>
@@ -891,10 +866,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>11</v>
@@ -902,38 +877,36 @@
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>76</v>
+      <c r="A14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>75</v>
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -941,7 +914,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>13</v>
@@ -952,10 +925,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -963,227 +936,227 @@
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>13</v>
@@ -1191,10 +1164,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>13</v>
@@ -1202,10 +1175,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>13</v>
@@ -1213,76 +1186,76 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>13</v>
@@ -1290,10 +1263,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>13</v>
@@ -1301,65 +1274,65 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>13</v>
@@ -1367,10 +1340,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>13</v>
@@ -1378,134 +1351,112 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>13</v>
+      <c r="A58" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>13</v>
+      <c r="A59" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="C60" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="C61" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="C62" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B63" s="6" t="s">
+      <c r="C63" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B65" s="6" t="s">
+      <c r="C65" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>25</v>
+      <c r="C66" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
